--- a/가톨릭관동대학교-26학년도-정시.xlsx
+++ b/가톨릭관동대학교-26학년도-정시.xlsx
@@ -35,14 +35,14 @@
     <sheet name="가톨릭관동대학교-26학년도-정시" sheetId="21" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'가톨릭관동대학교-26학년도-정시'!$A$1:$DJ$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'가톨릭관동대학교-26학년도-정시'!$A$1:$DJ$33</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2996" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2975" uniqueCount="433">
   <si>
     <t>비교대학 추가</t>
   </si>
@@ -1471,7 +1471,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -8464,7 +8464,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet21"/>
-  <dimension ref="A1:DC34"/>
+  <dimension ref="A1:DC33"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.3984375" bestFit="1" customWidth="1"/>
@@ -8858,60 +8858,56 @@
         <v>428</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>305</v>
+        <v>217</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>306</v>
+        <v>219</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>307</v>
+        <v>220</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>308</v>
+        <v>221</v>
       </c>
       <c r="K2" s="4">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
-      <c r="N2" s="4" t="s">
-        <v>309</v>
-      </c>
+      <c r="N2" s="4"/>
       <c r="O2" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>151</v>
-      </c>
+      <c r="T2" s="4"/>
       <c r="U2" s="4" t="s">
         <v>181</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="X2" s="4" t="s">
         <v>136</v>
@@ -8965,31 +8961,31 @@
       <c r="BI2" s="4"/>
       <c r="BJ2" s="4"/>
       <c r="BK2" s="4">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="BL2" s="4">
-        <v>115.5</v>
+        <v>192.5</v>
       </c>
       <c r="BM2" s="4">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="BN2" s="4">
-        <v>106.5</v>
+        <v>177.5</v>
       </c>
       <c r="BO2" s="4">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="BP2" s="4">
-        <v>97.5</v>
+        <v>162.5</v>
       </c>
       <c r="BQ2" s="4">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="BR2" s="4">
-        <v>88.5</v>
+        <v>147.5</v>
       </c>
       <c r="BS2" s="4">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="BT2" s="4">
         <v>10</v>
@@ -9054,69 +9050,69 @@
         <v>430</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>310</v>
+        <v>53</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>311</v>
+        <v>234</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>312</v>
+        <v>235</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>313</v>
+        <v>236</v>
       </c>
       <c r="K3" s="4">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="U3" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>260</v>
       </c>
       <c r="V3" s="4" t="s">
         <v>178</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>302</v>
+        <v>179</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>188</v>
+        <v>136</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
@@ -9125,22 +9121,24 @@
         <v>431</v>
       </c>
       <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
-      <c r="AF3" s="4"/>
+      <c r="AE3" s="4">
+        <v>20</v>
+      </c>
+      <c r="AF3" s="4">
+        <v>30</v>
+      </c>
       <c r="AG3" s="4">
+        <v>30</v>
+      </c>
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="4">
         <v>20</v>
       </c>
-      <c r="AH3" s="4"/>
-      <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="4"/>
       <c r="AL3" s="4"/>
-      <c r="AM3" s="4">
-        <v>40</v>
-      </c>
-      <c r="AN3" s="4">
-        <v>40</v>
-      </c>
+      <c r="AM3" s="4"/>
+      <c r="AN3" s="4"/>
       <c r="AO3" s="4"/>
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
@@ -9164,31 +9162,31 @@
       <c r="BI3" s="4"/>
       <c r="BJ3" s="4"/>
       <c r="BK3" s="4">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="BL3" s="4">
-        <v>115.5</v>
+        <v>288.75</v>
       </c>
       <c r="BM3" s="4">
-        <v>111</v>
+        <v>277.5</v>
       </c>
       <c r="BN3" s="4">
-        <v>106.5</v>
+        <v>266.25</v>
       </c>
       <c r="BO3" s="4">
-        <v>102</v>
+        <v>255</v>
       </c>
       <c r="BP3" s="4">
-        <v>97.5</v>
+        <v>243.75</v>
       </c>
       <c r="BQ3" s="4">
-        <v>93</v>
+        <v>232.5</v>
       </c>
       <c r="BR3" s="4">
-        <v>88.5</v>
+        <v>221.25</v>
       </c>
       <c r="BS3" s="4">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="BT3" s="4">
         <v>10</v>
@@ -9226,13 +9224,17 @@
       <c r="CI3" s="4"/>
       <c r="CJ3" s="4"/>
       <c r="CK3" s="4"/>
-      <c r="CL3" s="4"/>
+      <c r="CL3" s="4" t="s">
+        <v>432</v>
+      </c>
       <c r="CM3" s="4"/>
       <c r="CN3" s="4"/>
       <c r="CO3" s="4"/>
       <c r="CP3" s="4"/>
       <c r="CQ3" s="4"/>
-      <c r="CR3" s="4"/>
+      <c r="CR3" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CS3" s="4"/>
       <c r="CT3" s="4"/>
       <c r="CU3" s="4"/>
@@ -9253,43 +9255,43 @@
         <v>430</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>34</v>
+        <v>182</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>314</v>
+        <v>183</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>218</v>
+        <v>152</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>315</v>
+        <v>184</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>316</v>
+        <v>184</v>
       </c>
       <c r="K4" s="4">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
-      <c r="N4" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="O4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="P4" s="4" t="s">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>303</v>
+        <v>186</v>
       </c>
       <c r="R4" s="4" t="s">
         <v>136</v>
@@ -9297,21 +9299,21 @@
       <c r="S4" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="T4" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="U4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="V4" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
@@ -9359,31 +9361,31 @@
       <c r="BI4" s="4"/>
       <c r="BJ4" s="4"/>
       <c r="BK4" s="4">
+        <v>200</v>
+      </c>
+      <c r="BL4" s="4">
+        <v>192.5</v>
+      </c>
+      <c r="BM4" s="4">
+        <v>185</v>
+      </c>
+      <c r="BN4" s="4">
+        <v>177.5</v>
+      </c>
+      <c r="BO4" s="4">
+        <v>170</v>
+      </c>
+      <c r="BP4" s="4">
+        <v>162.5</v>
+      </c>
+      <c r="BQ4" s="4">
+        <v>155</v>
+      </c>
+      <c r="BR4" s="4">
+        <v>147.5</v>
+      </c>
+      <c r="BS4" s="4">
         <v>140</v>
-      </c>
-      <c r="BL4" s="4">
-        <v>134.75</v>
-      </c>
-      <c r="BM4" s="4">
-        <v>129.5</v>
-      </c>
-      <c r="BN4" s="4">
-        <v>124.25</v>
-      </c>
-      <c r="BO4" s="4">
-        <v>119</v>
-      </c>
-      <c r="BP4" s="4">
-        <v>113.75</v>
-      </c>
-      <c r="BQ4" s="4">
-        <v>108.5</v>
-      </c>
-      <c r="BR4" s="4">
-        <v>103.25</v>
-      </c>
-      <c r="BS4" s="4">
-        <v>98</v>
       </c>
       <c r="BT4" s="4">
         <v>10</v>
@@ -9448,65 +9450,63 @@
         <v>430</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K5" s="4">
         <v>1000</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4" t="s">
-        <v>163</v>
-      </c>
+      <c r="N5" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="O5" s="4"/>
       <c r="P5" s="4" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="T5" s="4"/>
+        <v>215</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>228</v>
+      </c>
       <c r="U5" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>203</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
       <c r="X5" s="4" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
@@ -9643,65 +9643,65 @@
         <v>430</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>257</v>
+        <v>189</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>258</v>
+        <v>192</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>259</v>
+        <v>193</v>
       </c>
       <c r="K6" s="4">
         <v>1000</v>
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="N6" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="O6" s="4"/>
       <c r="P6" s="4" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="R6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="S6" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="S6" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="U6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="V6" s="4" t="s">
         <v>194</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="X6" s="4" t="s">
         <v>136</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
@@ -9844,22 +9844,22 @@
         <v>5</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>53</v>
+        <v>283</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>234</v>
+        <v>144</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>139</v>
+        <v>284</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>236</v>
+        <v>286</v>
       </c>
       <c r="K7" s="4">
         <v>1000</v>
@@ -9869,38 +9869,32 @@
       <c r="N7" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="O7" s="4" t="s">
-        <v>237</v>
-      </c>
+      <c r="O7" s="4"/>
       <c r="P7" s="4" t="s">
-        <v>90</v>
+        <v>266</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="V7" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="W7" s="4" t="s">
-        <v>179</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
       <c r="X7" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4"/>
@@ -9909,24 +9903,22 @@
         <v>431</v>
       </c>
       <c r="AD7" s="4"/>
-      <c r="AE7" s="4">
+      <c r="AE7" s="4"/>
+      <c r="AF7" s="4"/>
+      <c r="AG7" s="4">
         <v>20</v>
       </c>
-      <c r="AF7" s="4">
-        <v>30</v>
-      </c>
-      <c r="AG7" s="4">
-        <v>30</v>
-      </c>
       <c r="AH7" s="4"/>
-      <c r="AI7" s="4">
-        <v>20</v>
-      </c>
+      <c r="AI7" s="4"/>
       <c r="AJ7" s="4"/>
       <c r="AK7" s="4"/>
       <c r="AL7" s="4"/>
-      <c r="AM7" s="4"/>
-      <c r="AN7" s="4"/>
+      <c r="AM7" s="4">
+        <v>40</v>
+      </c>
+      <c r="AN7" s="4">
+        <v>40</v>
+      </c>
       <c r="AO7" s="4"/>
       <c r="AP7" s="4"/>
       <c r="AQ7" s="4"/>
@@ -9950,31 +9942,31 @@
       <c r="BI7" s="4"/>
       <c r="BJ7" s="4"/>
       <c r="BK7" s="4">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="BL7" s="4">
-        <v>288.75</v>
+        <v>192.5</v>
       </c>
       <c r="BM7" s="4">
-        <v>277.5</v>
+        <v>185</v>
       </c>
       <c r="BN7" s="4">
-        <v>266.25</v>
+        <v>177.5</v>
       </c>
       <c r="BO7" s="4">
-        <v>255</v>
+        <v>170</v>
       </c>
       <c r="BP7" s="4">
-        <v>243.75</v>
+        <v>162.5</v>
       </c>
       <c r="BQ7" s="4">
-        <v>232.5</v>
+        <v>155</v>
       </c>
       <c r="BR7" s="4">
-        <v>221.25</v>
+        <v>147.5</v>
       </c>
       <c r="BS7" s="4">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="BT7" s="4">
         <v>10</v>
@@ -10012,17 +10004,13 @@
       <c r="CI7" s="4"/>
       <c r="CJ7" s="4"/>
       <c r="CK7" s="4"/>
-      <c r="CL7" s="4" t="s">
-        <v>432</v>
-      </c>
+      <c r="CL7" s="4"/>
       <c r="CM7" s="4"/>
       <c r="CN7" s="4"/>
       <c r="CO7" s="4"/>
       <c r="CP7" s="4"/>
       <c r="CQ7" s="4"/>
-      <c r="CR7" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CR7" s="4"/>
       <c r="CS7" s="4"/>
       <c r="CT7" s="4"/>
       <c r="CU7" s="4"/>
@@ -10043,65 +10031,65 @@
         <v>430</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>182</v>
+        <v>275</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>156</v>
+        <v>269</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>183</v>
+        <v>276</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>184</v>
+        <v>277</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>184</v>
+        <v>278</v>
       </c>
       <c r="K8" s="4">
         <v>1000</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4" t="s">
+      <c r="N8" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="P8" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4" t="s">
+      <c r="W8" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="V8" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="W8" s="4" t="s">
-        <v>186</v>
-      </c>
       <c r="X8" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
@@ -10244,22 +10232,22 @@
         <v>5</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>223</v>
+        <v>261</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="I9" s="4" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="K9" s="4">
         <v>1000</v>
@@ -10267,34 +10255,34 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>148</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
       <c r="R9" s="4" t="s">
         <v>136</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>215</v>
+        <v>141</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="U9" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
+        <v>204</v>
+      </c>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="X9" s="4" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
@@ -10437,22 +10425,22 @@
         <v>5</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>189</v>
+        <v>142</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>191</v>
+        <v>144</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="K10" s="4">
         <v>1000</v>
@@ -10460,33 +10448,33 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4" t="s">
-        <v>194</v>
+        <v>149</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="R10" s="4" t="s">
         <v>141</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="T10" s="4"/>
       <c r="U10" s="4" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>194</v>
+        <v>153</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="Y10" s="4" t="s">
         <v>156</v>
@@ -10626,28 +10614,28 @@
         <v>430</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>283</v>
+        <v>173</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>160</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>284</v>
+        <v>175</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>285</v>
+        <v>176</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>286</v>
+        <v>177</v>
       </c>
       <c r="K11" s="4">
         <v>1000</v>
@@ -10655,34 +10643,36 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="T11" s="4" t="s">
-        <v>202</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="T11" s="4"/>
       <c r="U11" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="V11" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="W11" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
       <c r="X11" s="4" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
@@ -10819,65 +10809,69 @@
         <v>430</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>269</v>
+        <v>175</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="K12" s="4">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="O12" s="4"/>
+        <v>309</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>136</v>
+      </c>
       <c r="P12" s="4" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="R12" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="S12" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="T12" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="U12" s="4"/>
+      <c r="U12" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="V12" s="4" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
@@ -10925,31 +10919,31 @@
       <c r="BI12" s="4"/>
       <c r="BJ12" s="4"/>
       <c r="BK12" s="4">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="BL12" s="4">
-        <v>192.5</v>
+        <v>115.5</v>
       </c>
       <c r="BM12" s="4">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="BN12" s="4">
-        <v>177.5</v>
+        <v>106.5</v>
       </c>
       <c r="BO12" s="4">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="BP12" s="4">
-        <v>162.5</v>
+        <v>97.5</v>
       </c>
       <c r="BQ12" s="4">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="BR12" s="4">
-        <v>147.5</v>
+        <v>88.5</v>
       </c>
       <c r="BS12" s="4">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="BT12" s="4">
         <v>10</v>
@@ -11014,63 +11008,69 @@
         <v>430</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>261</v>
+        <v>310</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>152</v>
+        <v>311</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>188</v>
+        <v>130</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>262</v>
+        <v>312</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>263</v>
+        <v>313</v>
       </c>
       <c r="K13" s="4">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4" t="s">
-        <v>140</v>
+        <v>229</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
+        <v>198</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>148</v>
+      </c>
       <c r="R13" s="4" t="s">
         <v>136</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="U13" s="4"/>
+        <v>143</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>260</v>
+      </c>
       <c r="V13" s="4" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>134</v>
+        <v>302</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>136</v>
+        <v>188</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
@@ -11118,31 +11118,31 @@
       <c r="BI13" s="4"/>
       <c r="BJ13" s="4"/>
       <c r="BK13" s="4">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="BL13" s="4">
-        <v>192.5</v>
+        <v>115.5</v>
       </c>
       <c r="BM13" s="4">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="BN13" s="4">
-        <v>177.5</v>
+        <v>106.5</v>
       </c>
       <c r="BO13" s="4">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="BP13" s="4">
-        <v>162.5</v>
+        <v>97.5</v>
       </c>
       <c r="BQ13" s="4">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="BR13" s="4">
-        <v>147.5</v>
+        <v>88.5</v>
       </c>
       <c r="BS13" s="4">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="BT13" s="4">
         <v>10</v>
@@ -11207,65 +11207,65 @@
         <v>430</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>142</v>
+        <v>267</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>146</v>
+        <v>268</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>147</v>
+        <v>268</v>
       </c>
       <c r="K14" s="4">
         <v>1000</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
-      <c r="N14" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="O14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4" t="s">
+        <v>195</v>
+      </c>
       <c r="P14" s="4" t="s">
-        <v>149</v>
+        <v>269</v>
       </c>
       <c r="Q14" s="4" t="s">
         <v>150</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="T14" s="4"/>
       <c r="U14" s="4" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>153</v>
+        <v>269</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
@@ -11402,28 +11402,28 @@
         <v>430</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>173</v>
+        <v>293</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>174</v>
+        <v>269</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>176</v>
+        <v>294</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>177</v>
+        <v>294</v>
       </c>
       <c r="K15" s="4">
         <v>1000</v>
@@ -11431,36 +11431,36 @@
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O15" s="4"/>
       <c r="P15" s="4" t="s">
-        <v>92</v>
+        <v>266</v>
       </c>
       <c r="Q15" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="R15" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="S15" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="T15" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="R15" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4" t="s">
-        <v>168</v>
-      </c>
+      <c r="U15" s="4"/>
       <c r="V15" s="4" t="s">
-        <v>134</v>
+        <v>266</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
@@ -11597,28 +11597,28 @@
         <v>430</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>267</v>
+        <v>164</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>165</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>268</v>
+        <v>166</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="K16" s="4">
         <v>1000</v>
@@ -11627,35 +11627,35 @@
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>269</v>
+        <v>169</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4" t="s">
-        <v>195</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="T16" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="U16" s="4"/>
       <c r="V16" s="4" t="s">
-        <v>269</v>
+        <v>169</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>188</v>
+        <v>136</v>
       </c>
       <c r="Z16" s="4"/>
       <c r="AA16" s="4"/>
@@ -11798,59 +11798,59 @@
         <v>5</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>293</v>
+        <v>247</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>207</v>
+        <v>150</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>294</v>
+        <v>249</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>294</v>
+        <v>250</v>
       </c>
       <c r="K17" s="4">
         <v>1000</v>
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
-      <c r="N17" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="O17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4" t="s">
+        <v>201</v>
+      </c>
       <c r="P17" s="4" t="s">
-        <v>266</v>
+        <v>203</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>179</v>
+        <v>251</v>
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="4" t="s">
-        <v>266</v>
+        <v>90</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>209</v>
+        <v>163</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>141</v>
+        <v>215</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
@@ -11987,60 +11987,56 @@
         <v>430</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>152</v>
+        <v>272</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>166</v>
+        <v>273</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>167</v>
+        <v>274</v>
       </c>
       <c r="K18" s="4">
         <v>1000</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
+      <c r="N18" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="O18" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q18" s="4" t="s">
         <v>148</v>
       </c>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
       <c r="R18" s="4" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="W18" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="U18" s="4" t="s">
         <v>135</v>
       </c>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
       <c r="X18" s="4" t="s">
         <v>136</v>
       </c>
@@ -12188,83 +12184,83 @@
         <v>5</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>247</v>
+        <v>120</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>175</v>
+        <v>239</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="K19" s="4">
         <v>1000</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
+      <c r="N19" s="4" t="s">
+        <v>243</v>
+      </c>
       <c r="O19" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q19" s="4" t="s">
-        <v>172</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
       <c r="R19" s="4" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="W19" s="4" t="s">
-        <v>163</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
       <c r="X19" s="4" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>152</v>
+        <v>207</v>
       </c>
       <c r="Z19" s="4"/>
       <c r="AA19" s="4"/>
-      <c r="AB19" s="4"/>
+      <c r="AB19" s="4" t="s">
+        <v>432</v>
+      </c>
       <c r="AC19" s="4" t="s">
         <v>431</v>
       </c>
       <c r="AD19" s="4"/>
-      <c r="AE19" s="4"/>
-      <c r="AF19" s="4"/>
+      <c r="AE19" s="4">
+        <v>20</v>
+      </c>
+      <c r="AF19" s="4">
+        <v>30</v>
+      </c>
       <c r="AG19" s="4">
         <v>20</v>
       </c>
       <c r="AH19" s="4"/>
-      <c r="AI19" s="4"/>
+      <c r="AI19" s="4">
+        <v>30</v>
+      </c>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="4"/>
       <c r="AL19" s="4"/>
-      <c r="AM19" s="4">
-        <v>40</v>
-      </c>
-      <c r="AN19" s="4">
-        <v>40</v>
-      </c>
+      <c r="AM19" s="4"/>
+      <c r="AN19" s="4"/>
       <c r="AO19" s="4"/>
       <c r="AP19" s="4"/>
       <c r="AQ19" s="4"/>
@@ -12350,13 +12346,17 @@
       <c r="CI19" s="4"/>
       <c r="CJ19" s="4"/>
       <c r="CK19" s="4"/>
-      <c r="CL19" s="4"/>
+      <c r="CL19" s="4" t="s">
+        <v>432</v>
+      </c>
       <c r="CM19" s="4"/>
       <c r="CN19" s="4"/>
       <c r="CO19" s="4"/>
       <c r="CP19" s="4"/>
       <c r="CQ19" s="4"/>
-      <c r="CR19" s="4"/>
+      <c r="CR19" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CS19" s="4"/>
       <c r="CT19" s="4"/>
       <c r="CU19" s="4"/>
@@ -12380,25 +12380,25 @@
         <v>427</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>271</v>
+        <v>120</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>272</v>
+        <v>323</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>273</v>
+        <v>324</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>274</v>
+        <v>324</v>
       </c>
       <c r="K20" s="4">
         <v>1000</v>
@@ -12406,56 +12406,60 @@
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>148</v>
+        <v>243</v>
       </c>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="V20" s="4"/>
       <c r="W20" s="4"/>
       <c r="X20" s="4" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="Z20" s="4"/>
       <c r="AA20" s="4"/>
-      <c r="AB20" s="4"/>
+      <c r="AB20" s="4" t="s">
+        <v>432</v>
+      </c>
       <c r="AC20" s="4" t="s">
         <v>431</v>
       </c>
       <c r="AD20" s="4"/>
-      <c r="AE20" s="4"/>
-      <c r="AF20" s="4"/>
+      <c r="AE20" s="4">
+        <v>20</v>
+      </c>
+      <c r="AF20" s="4">
+        <v>30</v>
+      </c>
       <c r="AG20" s="4">
         <v>20</v>
       </c>
       <c r="AH20" s="4"/>
-      <c r="AI20" s="4"/>
+      <c r="AI20" s="4">
+        <v>30</v>
+      </c>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="4"/>
       <c r="AL20" s="4"/>
-      <c r="AM20" s="4">
-        <v>40</v>
-      </c>
-      <c r="AN20" s="4">
-        <v>40</v>
-      </c>
+      <c r="AM20" s="4"/>
+      <c r="AN20" s="4"/>
       <c r="AO20" s="4"/>
       <c r="AP20" s="4"/>
       <c r="AQ20" s="4"/>
@@ -12541,13 +12545,17 @@
       <c r="CI20" s="4"/>
       <c r="CJ20" s="4"/>
       <c r="CK20" s="4"/>
-      <c r="CL20" s="4"/>
+      <c r="CL20" s="4" t="s">
+        <v>432</v>
+      </c>
       <c r="CM20" s="4"/>
       <c r="CN20" s="4"/>
       <c r="CO20" s="4"/>
       <c r="CP20" s="4"/>
       <c r="CQ20" s="4"/>
-      <c r="CR20" s="4"/>
+      <c r="CR20" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CS20" s="4"/>
       <c r="CT20" s="4"/>
       <c r="CU20" s="4"/>
@@ -12574,22 +12582,22 @@
         <v>5</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>120</v>
+        <v>287</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>90</v>
+        <v>175</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>241</v>
+        <v>289</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>242</v>
+        <v>290</v>
       </c>
       <c r="K21" s="4">
         <v>1000</v>
@@ -12597,60 +12605,60 @@
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
       <c r="N21" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>291</v>
+      </c>
       <c r="R21" s="4" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="T21" s="4" t="s">
-        <v>85</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="T21" s="4"/>
       <c r="U21" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
+        <v>291</v>
+      </c>
+      <c r="V21" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="W21" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="X21" s="4" t="s">
-        <v>207</v>
+        <v>136</v>
       </c>
       <c r="Y21" s="4" t="s">
-        <v>207</v>
+        <v>136</v>
       </c>
       <c r="Z21" s="4"/>
       <c r="AA21" s="4"/>
-      <c r="AB21" s="4" t="s">
-        <v>432</v>
-      </c>
+      <c r="AB21" s="4"/>
       <c r="AC21" s="4" t="s">
         <v>431</v>
       </c>
       <c r="AD21" s="4"/>
-      <c r="AE21" s="4">
-        <v>20</v>
-      </c>
-      <c r="AF21" s="4">
-        <v>30</v>
-      </c>
+      <c r="AE21" s="4"/>
+      <c r="AF21" s="4"/>
       <c r="AG21" s="4">
         <v>20</v>
       </c>
       <c r="AH21" s="4"/>
-      <c r="AI21" s="4">
-        <v>30</v>
-      </c>
+      <c r="AI21" s="4"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="4"/>
       <c r="AL21" s="4"/>
-      <c r="AM21" s="4"/>
-      <c r="AN21" s="4"/>
+      <c r="AM21" s="4">
+        <v>40</v>
+      </c>
+      <c r="AN21" s="4">
+        <v>40</v>
+      </c>
       <c r="AO21" s="4"/>
       <c r="AP21" s="4"/>
       <c r="AQ21" s="4"/>
@@ -12736,17 +12744,13 @@
       <c r="CI21" s="4"/>
       <c r="CJ21" s="4"/>
       <c r="CK21" s="4"/>
-      <c r="CL21" s="4" t="s">
-        <v>432</v>
-      </c>
+      <c r="CL21" s="4"/>
       <c r="CM21" s="4"/>
       <c r="CN21" s="4"/>
       <c r="CO21" s="4"/>
       <c r="CP21" s="4"/>
       <c r="CQ21" s="4"/>
-      <c r="CR21" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
       <c r="CT21" s="4"/>
       <c r="CU21" s="4"/>
@@ -12773,22 +12777,22 @@
         <v>5</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>288</v>
+        <v>174</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>175</v>
+        <v>269</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="K22" s="4">
         <v>1000</v>
@@ -12796,36 +12800,34 @@
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q22" s="4" t="s">
-        <v>291</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
       <c r="R22" s="4" t="s">
         <v>136</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="T22" s="4"/>
       <c r="U22" s="4" t="s">
-        <v>291</v>
+        <v>153</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>238</v>
+        <v>139</v>
       </c>
       <c r="W22" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="Z22" s="4"/>
       <c r="AA22" s="4"/>
@@ -12962,28 +12964,28 @@
         <v>430</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>269</v>
+        <v>130</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>281</v>
+        <v>212</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>282</v>
+        <v>213</v>
       </c>
       <c r="K23" s="4">
         <v>1000</v>
@@ -12991,34 +12993,32 @@
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
       <c r="R23" s="4" t="s">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="T23" s="4"/>
+        <v>156</v>
+      </c>
+      <c r="T23" s="4" t="s">
+        <v>216</v>
+      </c>
       <c r="U23" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="V23" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="W23" s="4" t="s">
-        <v>195</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
       <c r="X23" s="4" t="s">
         <v>156</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>152</v>
+        <v>207</v>
       </c>
       <c r="Z23" s="4"/>
       <c r="AA23" s="4"/>
@@ -13155,28 +13155,28 @@
         <v>430</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>211</v>
+        <v>296</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>212</v>
+        <v>297</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>213</v>
+        <v>297</v>
       </c>
       <c r="K24" s="4">
         <v>1000</v>
@@ -13184,32 +13184,36 @@
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="O24" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
+        <v>266</v>
+      </c>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="R24" s="4" t="s">
-        <v>215</v>
+        <v>141</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="U24" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="V24" s="4"/>
-      <c r="W24" s="4"/>
+        <v>266</v>
+      </c>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="W24" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="X24" s="4" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="Z24" s="4"/>
       <c r="AA24" s="4"/>
@@ -13349,59 +13353,59 @@
         <v>427</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>295</v>
+        <v>34</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>141</v>
+        <v>218</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="K25" s="4">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
       <c r="N25" s="4" t="s">
-        <v>266</v>
+        <v>137</v>
       </c>
       <c r="O25" s="4"/>
       <c r="P25" s="4" t="s">
-        <v>90</v>
+        <v>244</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>209</v>
+        <v>303</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>266</v>
+        <v>171</v>
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="W25" s="4" t="s">
         <v>209</v>
       </c>
       <c r="X25" s="4" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="Y25" s="4" t="s">
         <v>141</v>
@@ -13452,31 +13456,31 @@
       <c r="BI25" s="4"/>
       <c r="BJ25" s="4"/>
       <c r="BK25" s="4">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="BL25" s="4">
-        <v>192.5</v>
+        <v>134.75</v>
       </c>
       <c r="BM25" s="4">
-        <v>185</v>
+        <v>129.5</v>
       </c>
       <c r="BN25" s="4">
-        <v>177.5</v>
+        <v>124.25</v>
       </c>
       <c r="BO25" s="4">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="BP25" s="4">
-        <v>162.5</v>
+        <v>113.75</v>
       </c>
       <c r="BQ25" s="4">
-        <v>155</v>
+        <v>108.5</v>
       </c>
       <c r="BR25" s="4">
-        <v>147.5</v>
+        <v>103.25</v>
       </c>
       <c r="BS25" s="4">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="BT25" s="4">
         <v>10</v>
@@ -15087,208 +15091,8 @@
       <c r="DB33" s="4"/>
       <c r="DC33" s="4"/>
     </row>
-    <row r="34" spans="1:107" x14ac:dyDescent="0.4">
-      <c r="A34" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="K34" s="4">
-        <v>1000</v>
-      </c>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="O34" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="S34" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="T34" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="U34" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="V34" s="4"/>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y34" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="4"/>
-      <c r="AB34" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="AC34" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="AD34" s="4"/>
-      <c r="AE34" s="4">
-        <v>20</v>
-      </c>
-      <c r="AF34" s="4">
-        <v>30</v>
-      </c>
-      <c r="AG34" s="4">
-        <v>20</v>
-      </c>
-      <c r="AH34" s="4"/>
-      <c r="AI34" s="4">
-        <v>30</v>
-      </c>
-      <c r="AJ34" s="4"/>
-      <c r="AK34" s="4"/>
-      <c r="AL34" s="4"/>
-      <c r="AM34" s="4"/>
-      <c r="AN34" s="4"/>
-      <c r="AO34" s="4"/>
-      <c r="AP34" s="4"/>
-      <c r="AQ34" s="4"/>
-      <c r="AR34" s="4"/>
-      <c r="AS34" s="4"/>
-      <c r="AT34" s="4"/>
-      <c r="AU34" s="4"/>
-      <c r="AV34" s="4"/>
-      <c r="AW34" s="4"/>
-      <c r="AX34" s="4"/>
-      <c r="AY34" s="4"/>
-      <c r="AZ34" s="4"/>
-      <c r="BA34" s="4"/>
-      <c r="BB34" s="4"/>
-      <c r="BC34" s="4"/>
-      <c r="BD34" s="4"/>
-      <c r="BE34" s="4"/>
-      <c r="BF34" s="4"/>
-      <c r="BG34" s="4"/>
-      <c r="BH34" s="4"/>
-      <c r="BI34" s="4"/>
-      <c r="BJ34" s="4"/>
-      <c r="BK34" s="4">
-        <v>200</v>
-      </c>
-      <c r="BL34" s="4">
-        <v>192.5</v>
-      </c>
-      <c r="BM34" s="4">
-        <v>185</v>
-      </c>
-      <c r="BN34" s="4">
-        <v>177.5</v>
-      </c>
-      <c r="BO34" s="4">
-        <v>170</v>
-      </c>
-      <c r="BP34" s="4">
-        <v>162.5</v>
-      </c>
-      <c r="BQ34" s="4">
-        <v>155</v>
-      </c>
-      <c r="BR34" s="4">
-        <v>147.5</v>
-      </c>
-      <c r="BS34" s="4">
-        <v>140</v>
-      </c>
-      <c r="BT34" s="4">
-        <v>10</v>
-      </c>
-      <c r="BU34" s="4">
-        <v>10</v>
-      </c>
-      <c r="BV34" s="4">
-        <v>10</v>
-      </c>
-      <c r="BW34" s="4">
-        <v>10</v>
-      </c>
-      <c r="BX34" s="4">
-        <v>9.6</v>
-      </c>
-      <c r="BY34" s="4">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="BZ34" s="4">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="CA34" s="4">
-        <v>8.4</v>
-      </c>
-      <c r="CB34" s="4">
-        <v>8</v>
-      </c>
-      <c r="CC34" s="4"/>
-      <c r="CD34" s="4"/>
-      <c r="CE34" s="4"/>
-      <c r="CF34" s="4"/>
-      <c r="CG34" s="4"/>
-      <c r="CH34" s="4"/>
-      <c r="CI34" s="4"/>
-      <c r="CJ34" s="4"/>
-      <c r="CK34" s="4"/>
-      <c r="CL34" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="CM34" s="4"/>
-      <c r="CN34" s="4"/>
-      <c r="CO34" s="4"/>
-      <c r="CP34" s="4"/>
-      <c r="CQ34" s="4"/>
-      <c r="CR34" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="CS34" s="4"/>
-      <c r="CT34" s="4"/>
-      <c r="CU34" s="4"/>
-      <c r="CV34" s="4"/>
-      <c r="CW34" s="4"/>
-      <c r="CX34" s="4"/>
-      <c r="CY34" s="4"/>
-      <c r="CZ34" s="4"/>
-      <c r="DA34" s="4"/>
-      <c r="DB34" s="4"/>
-      <c r="DC34" s="4"/>
-    </row>
   </sheetData>
-  <sortState ref="A2:DJ34">
-    <sortCondition ref="D2:D34"/>
+  <sortState ref="A2:DC34">
     <sortCondition ref="E2:E34"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
